--- a/workspaces/instructivos/CHECK_LIST_ACTIVIDADES_GERENTE_COBRANZA_2025_LIMPIO.xlsx
+++ b/workspaces/instructivos/CHECK_LIST_ACTIVIDADES_GERENTE_COBRANZA_2025_LIMPIO.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -619,40 +619,26 @@
       <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>PCB1</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ASIGNACION, ENTREGA Y ARCHIVO DIARIO DE POLIZAS Y ENDOSOS</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>3.- ASIGNACION DIARIA DE POLIZAS / ENDOSOS</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>ACTUALIZADO 14/10/2025</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pagos: recepción/aplicación/ajustes y control de pagos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PCA4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>COBRO CON TARJETA TERMINAL KONFIO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -667,28 +653,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PCB2</t>
+          <t>PCB1</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>RECOLECCION  Y NOTIFICACION DE ENTREGA DE POLIZAS Y ENDOSOS</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Recoger pólizas del área de "Creación de Pólizas"</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
+          <t>ASIGNACION, ENTREGA Y ARCHIVO DIARIO DE POLIZAS Y ENDOSOS</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3.- ASIGNACION DIARIA DE POLIZAS / ENDOSOS</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>ACTUALIZADO 14/10/2025</t>
@@ -709,21 +689,21 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PCB3</t>
+          <t>PCB2</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE CONTROL, SUPERVISION DE RECIBOS</t>
+          <t>RECOLECCION  Y NOTIFICACION DE ENTREGA DE POLIZAS Y ENDOSOS</t>
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Realizar la supervision y llevar el control de los recibos faltantes de entrega</t>
+          <t>Recoger pólizas del área de "Creación de Pólizas"</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -733,27 +713,51 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 23/04/2026</t>
+          <t>ACTUALIZADO 14/10/2025</t>
         </is>
       </c>
       <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PCB3</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO DE CONTROL, SUPERVISION DE RECIBOS</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="2" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASIGNACION DE RECIBOS DE COBRO  </t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="3" t="n"/>
+          <t>Realizar la supervision y llevar el control de los recibos faltantes de entrega</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>ACTUALIZADO 23/04/2026</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
@@ -763,11 +767,11 @@
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>ASIGNACION DE AVISOS DE VISITA</t>
+          <t xml:space="preserve">ASIGNACION DE RECIBOS DE COBRO  </t>
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
@@ -775,61 +779,59 @@
       <c r="J9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>PCB4</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>CANCELACION DE POLIZAS</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>ASIGNACION DE AVISOS DE VISITA</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PCB4</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>CANCELACION DE POLIZAS</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Cancelacion de polizas</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>ACTUALIZADO 15/10/2025</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7.1.5</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Realizar cancelación en SIGA</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
     </row>
     <row r="12">
@@ -840,12 +842,12 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7.1.6</t>
+          <t>7.1.5</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Realizar cancelacion en CRM Proteg-rt</t>
+          <t>Realizar cancelación en SIGA</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -853,41 +855,23 @@
       <c r="J12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>PCB5</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>PARA LA CANCELACIÓN DE RECIBOS DE PAGO Y AVISOS DE VISITA</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="2" t="n">
-        <v>7.2</v>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7.1.6</t>
+        </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Cancelación de recibos de Pago y Avisos de Visita</t>
+          <t>Realizar cancelacion en CRM Proteg-rt</t>
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>ACTUALIZADO 30/10/2025</t>
-        </is>
-      </c>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
     </row>
     <row r="14">
@@ -903,25 +887,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PCB6</t>
+          <t>PCB5</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ATENCION GRUAS / ATENCION SINIESTROS</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>9.- ATENCION LINEAS DE EMERGENCIA</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="3" t="n"/>
+          <t>PARA LA CANCELACIÓN DE RECIBOS DE PAGO Y AVISOS DE VISITA</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Cancelación de recibos de Pago y Avisos de Visita</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTOS CABINA</t>
+          <t>ACTUALIZADO 30/10/2025</t>
         </is>
       </c>
       <c r="J14" s="3" t="n"/>
@@ -929,37 +915,35 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Cobradores: control operativo (tarjetas, asignación, gastos, etc.)</t>
+          <t>Documentos operativos: pólizas/endosos/recibos/avisos y control documental</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PCC1</t>
+          <t>PCB6</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ASIGNACION DE TARJETAS A COBRADORES Y VENDEDORES”</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>ASIGNACION DE TARJETAS DE COBRO A VENDEDORES Y COBRADORES</t>
-        </is>
-      </c>
+          <t>ATENCION GRUAS / ATENCION SINIESTROS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>9.- ATENCION LINEAS DE EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 23/10/2025</t>
+          <t>PROCEDIMIENTOS CABINA</t>
         </is>
       </c>
       <c r="J15" s="3" t="n"/>
@@ -977,27 +961,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PCC2</t>
+          <t>PCC1</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO PARA EL TRATAMIENTO DE TARJETAS DE COBRO</t>
+          <t>ASIGNACION DE TARJETAS A COBRADORES Y VENDEDORES”</t>
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="2" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Actualizacion Y Archivo de tarjetas Diarias</t>
+          <t>ASIGNACION DE TARJETAS DE COBRO A VENDEDORES Y COBRADORES</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>ACTUALLIZADO 08/11/2025</t>
+          <t>ACTUALIZADO 23/10/2025</t>
         </is>
       </c>
       <c r="J16" s="3" t="n"/>
@@ -1015,29 +999,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PCC3 (antes PC8)</t>
+          <t>PCC2</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>DEVOLUCION DE TARJETAS DE COBRO POR ATRASO (PC8)</t>
+          <t>PROCEDIMIENTO PARA EL TRATAMIENTO DE TARJETAS DE COBRO</t>
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7.1.1</t>
-        </is>
+      <c r="F17" s="2" t="n">
+        <v>6.1</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Recibir poliza o tarjeta a cancelar</t>
+          <t>Actualizacion Y Archivo de tarjetas Diarias</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 15/10/2025</t>
+          <t>ACTUALLIZADO 08/11/2025</t>
         </is>
       </c>
       <c r="J17" s="3" t="n"/>
@@ -1055,25 +1037,29 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PCC4</t>
+          <t>PCC3 (antes PC8)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ASIGNACIÓN DE COBRANZA QUINCENAL (COBRADORES)</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>15.- ASIGNACION DE COBRANZA QUINCENAL</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="3" t="n"/>
+          <t>DEVOLUCION DE TARJETAS DE COBRO POR ATRASO (PC8)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Recibir poliza o tarjeta a cancelar</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 11/11/2025</t>
+          <t>ACTUALIZADO 15/10/2025</t>
         </is>
       </c>
       <c r="J18" s="3" t="n"/>
@@ -1091,17 +1077,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PCC5</t>
+          <t>PCC4</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>REGISTRO DE GASTOS ANUAL DE MOTOCICLETAS DE COBRADORES</t>
+          <t>ASIGNACIÓN DE COBRANZA QUINCENAL (COBRADORES)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>23.- CONTROL DE GASTOS COBRADORES</t>
+          <t>15.- ASIGNACION DE COBRANZA QUINCENAL</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
@@ -1109,7 +1095,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 29/11/2025</t>
+          <t>ACTUALIZADO 11/11/2025</t>
         </is>
       </c>
       <c r="J19" s="3" t="n"/>
@@ -1117,27 +1103,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Vendedores: seguimiento y control de cobranza con vendedores</t>
+          <t>Cobradores: control operativo (tarjetas, asignación, gastos, etc.)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PCD1</t>
+          <t>PCC5</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEGUIMIENTO A COBRANZA ATRASADA</t>
+          <t>REGISTRO DE GASTOS ANUAL DE MOTOCICLETAS DE COBRADORES</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>25.- SEGUIMIENTO DE COBRANZA ATRASADA</t>
+          <t>23.- CONTROL DE GASTOS COBRADORES</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
@@ -1145,7 +1131,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 25/10/2025</t>
+          <t>ACTUALIZADO 29/11/2025</t>
         </is>
       </c>
       <c r="J20" s="3" t="n"/>
@@ -1153,27 +1139,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Contable/Finanzas: banco, conciliación, facturación, impuestos, nómina</t>
+          <t>Vendedores: seguimiento y control de cobranza con vendedores</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PCE1</t>
+          <t>PCD1</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>CAPTURA Y ACTUALIZACION DE DEPOSITOS / TRANSFERENCIAS DIARIOS</t>
+          <t>PROCEDIMIENTO DE SEGUIMIENTO A COBRANZA ATRASADA</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>4.- MOVIMIENTOS BANCARIOS DIARIOS</t>
+          <t>25.- SEGUIMIENTO DE COBRANZA ATRASADA</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
@@ -1181,7 +1167,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO Y REVISADO 14/10/2025</t>
+          <t>ACTUALIZADO 25/10/2025</t>
         </is>
       </c>
       <c r="J21" s="3" t="n"/>
@@ -1199,17 +1185,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PCE2</t>
+          <t>PCE1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>PARA LA GENERACION DEL FORMATO DE DISPERSION DE NOMINA</t>
+          <t>CAPTURA Y ACTUALIZACION DE DEPOSITOS / TRANSFERENCIAS DIARIOS</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>16.- DISPERSION DE NOMINA</t>
+          <t>4.- MOVIMIENTOS BANCARIOS DIARIOS</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
@@ -1217,7 +1203,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 13/10/2025</t>
+          <t>ACTUALIZADO Y REVISADO 14/10/2025</t>
         </is>
       </c>
       <c r="J22" s="3" t="n"/>
@@ -1235,17 +1221,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PCE3</t>
+          <t>PCE2</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ELABORACION DE LACONCILIACION BANCARIA</t>
+          <t>PARA LA GENERACION DEL FORMATO DE DISPERSION DE NOMINA</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>19.- CONCILIACION BANCARIA</t>
+          <t>16.- DISPERSION DE NOMINA</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -1253,7 +1239,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 27/11/2025</t>
+          <t>ACTUALIZADO 13/10/2025</t>
         </is>
       </c>
       <c r="J23" s="3" t="n"/>
@@ -1271,17 +1257,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>PCE4</t>
+          <t>PCE3</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>FACTURACIÓN MENSUAL DE INGRESOS BANCARIOS EN EFECTIVO (RFC GENERICO)</t>
+          <t>ELABORACION DE LACONCILIACION BANCARIA</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.- FACTURACION DE INGRESOS </t>
+          <t>19.- CONCILIACION BANCARIA</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
@@ -1289,7 +1275,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 21/10/2025</t>
+          <t>ACTUALIZADO 27/11/2025</t>
         </is>
       </c>
       <c r="J24" s="3" t="n"/>
@@ -1307,17 +1293,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PCE5</t>
+          <t>PCE4</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>FACTURACION DE CAJA CHICA</t>
+          <t>FACTURACIÓN MENSUAL DE INGRESOS BANCARIOS EN EFECTIVO (RFC GENERICO)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>21.- GASTOS CAJA CHICA</t>
+          <t xml:space="preserve">20.- FACTURACION DE INGRESOS </t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
@@ -1325,7 +1311,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 27/11/2025</t>
+          <t>ACTUALIZADO 21/10/2025</t>
         </is>
       </c>
       <c r="J25" s="3" t="n"/>
@@ -1343,17 +1329,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>PCE6</t>
+          <t>PCE5</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>PARA LA FACTURACIÓN DE PAGOS DE IMPUESTOS</t>
+          <t>FACTURACION DE CAJA CHICA</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.- FACTURACION IMPUESTOS </t>
+          <t>21.- GASTOS CAJA CHICA</t>
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
@@ -1361,7 +1347,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 29/10/2025</t>
+          <t>ACTUALIZADO 27/11/2025</t>
         </is>
       </c>
       <c r="J26" s="3" t="n"/>
@@ -1369,27 +1355,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Reportes: generación de reportes/entregables (comisiones, mensual, etc.)</t>
+          <t>Contable/Finanzas: banco, conciliación, facturación, impuestos, nómina</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PCF1</t>
+          <t>PCE6</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>PARA LA REALIZACION DEL REPORTE DE COMISIONES QUINCENALES DE VENDEDORES</t>
+          <t>PARA LA FACTURACIÓN DE PAGOS DE IMPUESTOS</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>12.- REPORTE COMISIONES QUINCENALES VENDEDORES</t>
+          <t xml:space="preserve">24.- FACTURACION IMPUESTOS </t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
@@ -1415,17 +1401,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>PCF2</t>
+          <t>PCF1</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>PARA REPORTE Y PAGO DE COMISIONES QUINCENALES A COBRADORES</t>
+          <t>PARA LA REALIZACION DEL REPORTE DE COMISIONES QUINCENALES DE VENDEDORES</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>13.- REPORTE COMISIONES QUINCENALES COBRADORES</t>
+          <t>12.- REPORTE COMISIONES QUINCENALES VENDEDORES</t>
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
@@ -1433,7 +1419,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>ACTUALIZADO 17/10/2025</t>
+          <t>ACTUALIZADO 29/10/2025</t>
         </is>
       </c>
       <c r="J28" s="3" t="n"/>
@@ -1451,17 +1437,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>PCF3</t>
+          <t>PCF2</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>PARA LA GENERACION DE REPORTE MENSUAL DE COBRANZA</t>
+          <t>PARA REPORTE Y PAGO DE COMISIONES QUINCENALES A COBRADORES</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>17.- REPORTE MENSUAL DE COBRANZA</t>
+          <t>13.- REPORTE COMISIONES QUINCENALES COBRADORES</t>
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
@@ -1469,10 +1455,46 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t>ACTUALIZADO 17/10/2025</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Reportes: generación de reportes/entregables (comisiones, mensual, etc.)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PCF3</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>PARA LA GENERACION DE REPORTE MENSUAL DE COBRANZA</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>17.- REPORTE MENSUAL DE COBRANZA</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
           <t>ACTUALIZADO 14/10/2025</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
